--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>-38.461538461538</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
         <v>39</v>
       </c>
       <c r="H16" s="15">
-        <v>-28.205128205128</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="I16" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.272727272727</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="L16" s="15">
-        <v>30.303030303030</v>
+        <v>50</v>
       </c>
       <c r="M16" s="15">
-        <v>4.878048780487</v>
+        <v>15.909090909090</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.868525896414</v>
+        <v>-82.653061224489</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-35</v>
+        <v>6.25</v>
       </c>
       <c r="F17" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G17" s="14">
         <v>65</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.384615384615</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I17" s="14">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="J17" s="14">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.325581395348</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>5</v>
+        <v>4.081632653061</v>
       </c>
       <c r="M17" s="15">
-        <v>127.027027027027</v>
+        <v>131.818181818182</v>
       </c>
       <c r="N17" s="15">
-        <v>-23.636363636363</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
+        <v>18.181818181818</v>
+      </c>
+      <c r="I18" s="14">
+        <v>26</v>
+      </c>
+      <c r="J18" s="14">
         <v>16</v>
       </c>
-      <c r="G18" s="14">
-        <v>9</v>
-      </c>
-      <c r="H18" s="15">
-        <v>77.777777777777</v>
-      </c>
-      <c r="I18" s="14">
-        <v>24</v>
-      </c>
-      <c r="J18" s="14">
-        <v>13</v>
-      </c>
       <c r="K18" s="15">
-        <v>84.615384615384</v>
+        <v>62.5</v>
       </c>
       <c r="L18" s="15">
-        <v>4.347826086956</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.241379310344</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.438247011952</v>
+        <v>-90.812720848056</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>7.692307692307</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.578947368421</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J19" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.895522388059</v>
+        <v>-22.368421052631</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.188405797101</v>
+        <v>-32.183908045977</v>
       </c>
       <c r="M19" s="15">
-        <v>120.833333333333</v>
+        <v>110.714285714286</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.039215686274</v>
+        <v>-51.639344262295</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-36.363636363636</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" s="15">
-        <v>-24</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>72.727272727272</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-81</v>
+        <v>-82.905982905982</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.867924528301</v>
+        <v>-17.5</v>
       </c>
       <c r="F21" s="17">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G21" s="17">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.587628865979</v>
+        <v>-16.111111111111</v>
       </c>
       <c r="I21" s="17">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="J21" s="17">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.201680672268</v>
+        <v>-5.035971223021</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>-3.649635036496</v>
       </c>
       <c r="M21" s="18">
-        <v>59.440559440559</v>
+        <v>61.963190184049</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.397094430992</v>
+        <v>-72.151898734177</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,20 +1220,20 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
         <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>2</v>
       </c>
       <c r="H23" s="15">
         <v>100</v>
@@ -1248,7 +1248,7 @@
         <v>100</v>
       </c>
       <c r="L23" s="15">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="M23" s="15">
         <v>100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>5.882352941176</v>
+        <v>73.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H24" s="15">
-        <v>27.941176470588</v>
+        <v>39.682539682539</v>
       </c>
       <c r="I24" s="14">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="J24" s="14">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="K24" s="15">
-        <v>21.276595744680</v>
+        <v>27.522935779816</v>
       </c>
       <c r="L24" s="15">
-        <v>26.666666666666</v>
+        <v>27.522935779816</v>
       </c>
       <c r="M24" s="15">
-        <v>7.547169811320</v>
+        <v>15.833333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.076923076923</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.222222222222</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L25" s="15">
-        <v>-30</v>
+        <v>-4</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>142.857142857143</v>
+        <v>26.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G26" s="14">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>37.037037037037</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>33.333333333333</v>
+        <v>31.111111111111</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.259842519685</v>
+        <v>-25.786163522012</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.660377358490</v>
+        <v>-12.592592592592</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="15">
+        <v>40</v>
+      </c>
+      <c r="I28" s="14">
+        <v>13</v>
+      </c>
+      <c r="J28" s="14">
         <v>9</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
-      <c r="H28" s="15">
-        <v>28.571428571428</v>
-      </c>
-      <c r="I28" s="14">
-        <v>14</v>
-      </c>
-      <c r="J28" s="14">
-        <v>8</v>
-      </c>
       <c r="K28" s="15">
-        <v>75</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -911,22 +911,22 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>150</v>
+      </c>
+      <c r="M15" s="15">
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-36.363636363636</v>
+        <v>60</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G16" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.897435897435</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J16" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.272727272727</v>
+        <v>1.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>50</v>
+        <v>56.410256410256</v>
       </c>
       <c r="M16" s="15">
-        <v>15.909090909090</v>
+        <v>15.094339622641</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.653061224489</v>
+        <v>-82.111436950146</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>6.25</v>
+        <v>125</v>
       </c>
       <c r="F17" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.692307692307</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I17" s="14">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>10.909090909090</v>
       </c>
       <c r="L17" s="15">
-        <v>4.081632653061</v>
+        <v>11.926605504587</v>
       </c>
       <c r="M17" s="15">
-        <v>131.818181818182</v>
+        <v>130.188679245283</v>
       </c>
       <c r="N17" s="15">
-        <v>-15</v>
+        <v>-6.870229007633</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>62.5</v>
+        <v>57.894736842105</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.703703703703</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.529411764705</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.812720848056</v>
+        <v>-90.625</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>137.5</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>16.279069767441</v>
       </c>
       <c r="I19" s="14">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="J19" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.368421052631</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.183908045977</v>
+        <v>-19</v>
       </c>
       <c r="M19" s="15">
-        <v>110.714285714286</v>
+        <v>153.125</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.639344262295</v>
+        <v>-37.209302325581</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.666666666666</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="M20" s="15">
-        <v>66.666666666666</v>
+        <v>69.230769230769</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.905982905982</v>
+        <v>-85.620915032679</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.5</v>
+        <v>85.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="G21" s="17">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.111111111111</v>
+        <v>4.294478527607</v>
       </c>
       <c r="I21" s="17">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="J21" s="17">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.035971223021</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.649635036496</v>
+        <v>1.572327044025</v>
       </c>
       <c r="M21" s="18">
-        <v>61.963190184049</v>
+        <v>70.899470899470</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.151898734177</v>
+        <v>-70.339761248852</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>50</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>250</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="J22" s="14">
+        <v>2</v>
+      </c>
+      <c r="K22" s="15">
+        <v>400</v>
       </c>
       <c r="L22" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
         <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>73.333333333333</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F24" s="14">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>39.682539682539</v>
+        <v>21.875</v>
       </c>
       <c r="I24" s="14">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="J24" s="14">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="K24" s="15">
-        <v>27.522935779816</v>
+        <v>23.015873015873</v>
       </c>
       <c r="L24" s="15">
-        <v>27.522935779816</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M24" s="15">
-        <v>15.833333333333</v>
+        <v>9.154929577464</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
         <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J25" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="L25" s="15">
-        <v>-4</v>
+        <v>-12.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14">
         <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>26.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>37.037037037037</v>
+        <v>53.191489361702</v>
       </c>
       <c r="I26" s="14">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K26" s="15">
-        <v>31.111111111111</v>
+        <v>27.619047619047</v>
       </c>
       <c r="L26" s="15">
-        <v>-25.786163522012</v>
+        <v>-23.428571428571</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.592592592592</v>
+        <v>-12.418300653594</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.473684210526</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.235294117647</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -879,45 +879,45 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M14" s="15">
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
         <v>150</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G16" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.888888888888</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J16" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>1.666666666666</v>
+        <v>6.060606060606</v>
       </c>
       <c r="L16" s="15">
-        <v>56.410256410256</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>15.094339622641</v>
+        <v>14.754098360655</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.111436950146</v>
+        <v>-81.912144702842</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G17" s="14">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>10.526315789473</v>
+        <v>17.857142857142</v>
       </c>
       <c r="I17" s="14">
+        <v>137</v>
+      </c>
+      <c r="J17" s="14">
         <v>122</v>
       </c>
-      <c r="J17" s="14">
-        <v>110</v>
-      </c>
       <c r="K17" s="15">
-        <v>10.909090909090</v>
+        <v>12.295081967213</v>
       </c>
       <c r="L17" s="15">
-        <v>11.926605504587</v>
+        <v>9.6</v>
       </c>
       <c r="M17" s="15">
-        <v>130.188679245283</v>
+        <v>140.350877192982</v>
       </c>
       <c r="N17" s="15">
-        <v>-6.870229007633</v>
+        <v>-6.802721088435</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
         <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>57.894736842105</v>
+        <v>37.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>-17.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.625</v>
+        <v>-90.807799442896</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
+        <v>20</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-45</v>
+      </c>
+      <c r="F19" s="14">
+        <v>54</v>
+      </c>
+      <c r="G19" s="14">
+        <v>50</v>
+      </c>
+      <c r="H19" s="15">
         <v>8</v>
       </c>
-      <c r="E19" s="15">
-        <v>137.5</v>
-      </c>
-      <c r="F19" s="14">
-        <v>50</v>
-      </c>
-      <c r="G19" s="14">
-        <v>43</v>
-      </c>
-      <c r="H19" s="15">
-        <v>16.279069767441</v>
-      </c>
       <c r="I19" s="14">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J19" s="14">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.571428571428</v>
+        <v>-8.653846153846</v>
       </c>
       <c r="L19" s="15">
-        <v>-19</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>153.125</v>
+        <v>163.888888888889</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.209302325581</v>
+        <v>-34.027777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-30.769230769230</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.666666666666</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.032258064516</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="M20" s="15">
-        <v>69.230769230769</v>
+        <v>27.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.620915032679</v>
+        <v>-87.362637362637</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>85.714285714285</v>
+        <v>-18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G21" s="17">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H21" s="18">
-        <v>4.294478527607</v>
+        <v>4.733727810650</v>
       </c>
       <c r="I21" s="17">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="J21" s="17">
-        <v>306</v>
+        <v>354</v>
       </c>
       <c r="K21" s="18">
-        <v>5.555555555555</v>
+        <v>3.107344632768</v>
       </c>
       <c r="L21" s="18">
-        <v>1.572327044025</v>
+        <v>0.550964187327</v>
       </c>
       <c r="M21" s="18">
-        <v>70.899470899470</v>
+        <v>71.361502347417</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.339761248852</v>
+        <v>-70.445344129554</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>50</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>7</v>
@@ -1207,7 +1207,7 @@
         <v>400</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>100</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="L23" s="15">
         <v>75</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>17</v>
+      </c>
+      <c r="D24" s="14">
         <v>15</v>
       </c>
-      <c r="D24" s="14">
-        <v>17</v>
-      </c>
       <c r="E24" s="15">
-        <v>-11.764705882352</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
         <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>21.875</v>
+        <v>18.75</v>
       </c>
       <c r="I24" s="14">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J24" s="14">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K24" s="15">
-        <v>23.015873015873</v>
+        <v>21.985815602836</v>
       </c>
       <c r="L24" s="15">
-        <v>14.814814814814</v>
+        <v>8.176100628930</v>
       </c>
       <c r="M24" s="15">
-        <v>9.154929577464</v>
+        <v>7.5</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
         <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>42.857142857142</v>
+        <v>53.846153846153</v>
       </c>
       <c r="I25" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.5</v>
+        <v>-22.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>53.191489361702</v>
+        <v>7.936507936507</v>
       </c>
       <c r="I26" s="14">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J26" s="14">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="K26" s="15">
-        <v>27.619047619047</v>
+        <v>15.267175572519</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.428571428571</v>
+        <v>-21.761658031088</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.418300653594</v>
+        <v>-9.036144578313</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="L27" s="15">
         <v>16.666666666666</v>
@@ -1435,10 +1435,10 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-75</v>
@@ -1535,7 +1535,7 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
         <v>-75</v>

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -882,7 +882,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
         <v>-80</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
+        <v>7</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>-2.857142857142</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I16" s="14">
+        <v>73</v>
+      </c>
+      <c r="J16" s="14">
         <v>70</v>
       </c>
-      <c r="J16" s="14">
-        <v>66</v>
-      </c>
       <c r="K16" s="15">
-        <v>6.060606060606</v>
+        <v>4.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>55.555555555555</v>
+        <v>46</v>
       </c>
       <c r="M16" s="15">
-        <v>14.754098360655</v>
+        <v>7.352941176470</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.912144702842</v>
+        <v>-83.101851851851</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>-43.75</v>
       </c>
       <c r="F17" s="14">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H17" s="15">
-        <v>17.857142857142</v>
+        <v>19.230769230769</v>
       </c>
       <c r="I17" s="14">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="J17" s="14">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="K17" s="15">
-        <v>12.295081967213</v>
+        <v>7.246376811594</v>
       </c>
       <c r="L17" s="15">
-        <v>9.6</v>
+        <v>9.629629629629</v>
       </c>
       <c r="M17" s="15">
-        <v>140.350877192982</v>
+        <v>124.242424242424</v>
       </c>
       <c r="N17" s="15">
-        <v>-6.802721088435</v>
+        <v>-12.941176470588</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>37.5</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.5</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="M18" s="15">
-        <v>-15.384615384615</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.807799442896</v>
+        <v>-90.537084398977</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>9</v>
+      </c>
+      <c r="D19" s="14">
         <v>11</v>
       </c>
-      <c r="D19" s="14">
-        <v>20</v>
-      </c>
       <c r="E19" s="15">
-        <v>-45</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J19" s="14">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.653846153846</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.666666666666</v>
+        <v>-16</v>
       </c>
       <c r="M19" s="15">
-        <v>163.888888888889</v>
+        <v>138.636363636364</v>
       </c>
       <c r="N19" s="15">
-        <v>-34.027777777777</v>
+        <v>-37.125748502994</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.352941176470</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.352941176470</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="M20" s="15">
-        <v>27.777777777777</v>
+        <v>27.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.362637362637</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.75</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F21" s="17">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="G21" s="17">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H21" s="18">
-        <v>4.733727810650</v>
+        <v>6.493506493506</v>
       </c>
       <c r="I21" s="17">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="J21" s="17">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="K21" s="18">
-        <v>3.107344632768</v>
+        <v>2.040816326530</v>
       </c>
       <c r="L21" s="18">
-        <v>0.550964187327</v>
+        <v>0.755667506297</v>
       </c>
       <c r="M21" s="18">
-        <v>71.361502347417</v>
+        <v>65.289256198347</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.445344129554</v>
+        <v>-71.181556195965</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
+        <v>3</v>
+      </c>
+      <c r="G23" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L23" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="M23" s="15">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>13.333333333333</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H24" s="15">
-        <v>18.75</v>
+        <v>35.593220338983</v>
       </c>
       <c r="I24" s="14">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="J24" s="14">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K24" s="15">
-        <v>21.985815602836</v>
+        <v>26.797385620915</v>
       </c>
       <c r="L24" s="15">
-        <v>8.176100628930</v>
+        <v>3.191489361702</v>
       </c>
       <c r="M24" s="15">
-        <v>7.5</v>
+        <v>8.988764044943</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
         <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>53.846153846153</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I25" s="14">
+        <v>32</v>
+      </c>
+      <c r="J25" s="14">
         <v>31</v>
       </c>
-      <c r="J25" s="14">
-        <v>29</v>
-      </c>
       <c r="K25" s="15">
-        <v>6.896551724137</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.5</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-34.615384615384</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F26" s="14">
+        <v>81</v>
+      </c>
+      <c r="G26" s="14">
         <v>68</v>
       </c>
-      <c r="G26" s="14">
-        <v>63</v>
-      </c>
       <c r="H26" s="15">
-        <v>7.936507936507</v>
+        <v>19.117647058823</v>
       </c>
       <c r="I26" s="14">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="J26" s="14">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K26" s="15">
-        <v>15.267175572519</v>
+        <v>25.174825174825</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.761658031088</v>
+        <v>-16.355140186915</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.036144578313</v>
+        <v>-7.253886010362</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>6</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>500</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>70</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -879,51 +879,51 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="N15" s="15">
         <v>-12.5</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>7.692307692307</v>
+        <v>47.619047619047</v>
       </c>
       <c r="I16" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="J16" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K16" s="15">
-        <v>4.285714285714</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L16" s="15">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M16" s="15">
-        <v>7.352941176470</v>
+        <v>12</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.101851851851</v>
+        <v>-82.426778242677</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E17" s="15">
-        <v>-43.75</v>
+        <v>-32</v>
       </c>
       <c r="F17" s="14">
         <v>62</v>
       </c>
       <c r="G17" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H17" s="15">
-        <v>19.230769230769</v>
+        <v>1.639344262295</v>
       </c>
       <c r="I17" s="14">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="J17" s="14">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="K17" s="15">
-        <v>7.246376811594</v>
+        <v>2.453987730061</v>
       </c>
       <c r="L17" s="15">
-        <v>9.629629629629</v>
+        <v>13.605442176870</v>
       </c>
       <c r="M17" s="15">
-        <v>124.242424242424</v>
+        <v>128.767123287671</v>
       </c>
       <c r="N17" s="15">
-        <v>-12.941176470588</v>
+        <v>-8.743169398907</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-13.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>32.142857142857</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.909090909090</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="M18" s="15">
-        <v>-5.128205128205</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.537084398977</v>
+        <v>-89.099526066350</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I19" s="14">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="J19" s="14">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.695652173913</v>
+        <v>-6.299212598425</v>
       </c>
       <c r="L19" s="15">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="M19" s="15">
-        <v>138.636363636364</v>
+        <v>153.191489361702</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.125748502994</v>
+        <v>-33.519553072625</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-18.181818181818</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.222222222222</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.324324324324</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="M20" s="15">
-        <v>27.272727272727</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.666666666666</v>
+        <v>-84.821428571428</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.789473684210</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F21" s="17">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="G21" s="17">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H21" s="18">
-        <v>6.493506493506</v>
+        <v>11.515151515151</v>
       </c>
       <c r="I21" s="17">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="J21" s="17">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="K21" s="18">
-        <v>2.040816326530</v>
+        <v>3.611738148984</v>
       </c>
       <c r="L21" s="18">
-        <v>0.755667506297</v>
+        <v>3.146067415730</v>
       </c>
       <c r="M21" s="18">
-        <v>65.289256198347</v>
+        <v>73.207547169811</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.181556195965</v>
+        <v>-69.521912350597</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>450</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L22" s="15">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M22" s="15">
         <v>120</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>4</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I23" s="14">
+        <v>10</v>
+      </c>
+      <c r="J23" s="14">
+        <v>6</v>
+      </c>
+      <c r="K23" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="L23" s="15">
+        <v>150</v>
+      </c>
+      <c r="M23" s="15">
         <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>3</v>
-      </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="15">
-        <v>50</v>
-      </c>
-      <c r="I23" s="14">
-        <v>9</v>
-      </c>
-      <c r="J23" s="14">
-        <v>5</v>
-      </c>
-      <c r="K23" s="15">
-        <v>80</v>
-      </c>
-      <c r="L23" s="15">
-        <v>125</v>
-      </c>
-      <c r="M23" s="15">
-        <v>125</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>83.333333333333</v>
+        <v>92.307692307692</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>35.593220338983</v>
+        <v>36.842105263157</v>
       </c>
       <c r="I24" s="14">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="J24" s="14">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="K24" s="15">
-        <v>26.797385620915</v>
+        <v>31.325301204819</v>
       </c>
       <c r="L24" s="15">
-        <v>3.191489361702</v>
+        <v>7.920792079207</v>
       </c>
       <c r="M24" s="15">
-        <v>8.988764044943</v>
+        <v>11.794871794871</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>38.461538461538</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>3.225806451612</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.888888888888</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>133.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G26" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H26" s="15">
-        <v>19.117647058823</v>
+        <v>30.985915492957</v>
       </c>
       <c r="I26" s="14">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="J26" s="14">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="K26" s="15">
-        <v>25.174825174825</v>
+        <v>29.192546583850</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.355140186915</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.253886010362</v>
+        <v>-3.255813953488</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>5</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
         <v>25</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
-      </c>
-      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>500</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L28" s="15">
-        <v>13.333333333333</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,7 +1494,7 @@
         <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
         <v>-75</v>
@@ -1535,7 +1535,7 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M30" s="15">
         <v>-75</v>

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -879,54 +879,54 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>3</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I15" s="14">
+        <v>10</v>
+      </c>
+      <c r="J15" s="14">
         <v>7</v>
       </c>
-      <c r="J15" s="14">
-        <v>6</v>
-      </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>233.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-12.5</v>
+        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>83.333333333333</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G16" s="14">
         <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>47.619047619047</v>
+        <v>61.904761904761</v>
       </c>
       <c r="I16" s="14">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J16" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K16" s="15">
-        <v>10.526315789473</v>
+        <v>17.283950617283</v>
       </c>
       <c r="L16" s="15">
-        <v>40</v>
+        <v>48.4375</v>
       </c>
       <c r="M16" s="15">
-        <v>12</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.426778242677</v>
+        <v>-82.109227871939</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>-32</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G17" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H17" s="15">
-        <v>1.639344262295</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="I17" s="14">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="J17" s="14">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="K17" s="15">
-        <v>2.453987730061</v>
+        <v>6.077348066298</v>
       </c>
       <c r="L17" s="15">
-        <v>13.605442176870</v>
+        <v>23.870967741935</v>
       </c>
       <c r="M17" s="15">
-        <v>128.767123287671</v>
+        <v>137.037037037037</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.743169398907</v>
+        <v>-4.477611940298</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
         <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
+        <v>25</v>
+      </c>
+      <c r="I18" s="14">
+        <v>50</v>
+      </c>
+      <c r="J18" s="14">
+        <v>35</v>
+      </c>
+      <c r="K18" s="15">
         <v>42.857142857142</v>
       </c>
-      <c r="I18" s="14">
-        <v>46</v>
-      </c>
-      <c r="J18" s="14">
-        <v>30</v>
-      </c>
-      <c r="K18" s="15">
-        <v>53.333333333333</v>
-      </c>
       <c r="L18" s="15">
-        <v>-6.122448979591</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>9.523809523809</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.099526066350</v>
+        <v>-89.384288747346</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>5.882352941176</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I19" s="14">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.299212598425</v>
+        <v>-7.534246575342</v>
       </c>
       <c r="L19" s="15">
-        <v>-15</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="M19" s="15">
-        <v>153.191489361702</v>
+        <v>159.615384615385</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.519553072625</v>
+        <v>-29.319371727748</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>6</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-6.666666666666</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I20" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.073170731707</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.073170731707</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="M20" s="15">
-        <v>41.666666666666</v>
+        <v>54.166666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.821428571428</v>
+        <v>-84.647302904564</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>55</v>
+      </c>
+      <c r="D21" s="17">
         <v>54</v>
       </c>
-      <c r="D21" s="17">
-        <v>51</v>
-      </c>
       <c r="E21" s="18">
-        <v>5.882352941176</v>
+        <v>1.851851851851</v>
       </c>
       <c r="F21" s="17">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G21" s="17">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="H21" s="18">
-        <v>11.515151515151</v>
+        <v>1.047120418848</v>
       </c>
       <c r="I21" s="17">
-        <v>459</v>
+        <v>521</v>
       </c>
       <c r="J21" s="17">
-        <v>443</v>
+        <v>497</v>
       </c>
       <c r="K21" s="18">
-        <v>3.611738148984</v>
+        <v>4.828973843058</v>
       </c>
       <c r="L21" s="18">
-        <v>3.146067415730</v>
+        <v>6.762295081967</v>
       </c>
       <c r="M21" s="18">
-        <v>73.207547169811</v>
+        <v>79.037800687285</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.521912350597</v>
+        <v>-68.595539481615</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
-      </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>66.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>150</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M23" s="15">
         <v>100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>92.307692307692</v>
+        <v>26.315789473684</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H24" s="15">
-        <v>36.842105263157</v>
+        <v>52.542372881355</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="J24" s="14">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>31.325301204819</v>
+        <v>32.432432432432</v>
       </c>
       <c r="L24" s="15">
-        <v>7.920792079207</v>
+        <v>15.023474178403</v>
       </c>
       <c r="M24" s="15">
-        <v>11.794871794871</v>
+        <v>15.023474178403</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.702702702702</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.404255319148</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="F26" s="14">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H26" s="15">
-        <v>30.985915492957</v>
+        <v>17.948717948717</v>
       </c>
       <c r="I26" s="14">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="J26" s="14">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="K26" s="15">
-        <v>29.192546583850</v>
+        <v>24.043715846994</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.276679841897</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.255813953488</v>
+        <v>-8.835341365461</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>600</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>80</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>5.882352941176</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
+        <v>11</v>
+      </c>
+      <c r="J15" s="14">
         <v>10</v>
       </c>
-      <c r="J15" s="14">
-        <v>7</v>
-      </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>10</v>
       </c>
       <c r="L15" s="15">
-        <v>233.333333333333</v>
+        <v>175</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="N15" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>120</v>
+        <v>266.666666666667</v>
       </c>
       <c r="F16" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>61.904761904761</v>
+        <v>111.111111111111</v>
       </c>
       <c r="I16" s="14">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J16" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K16" s="15">
-        <v>17.283950617283</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>48.4375</v>
+        <v>54.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>11.764705882352</v>
+        <v>13.684210526315</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.109227871939</v>
+        <v>-81.085814360770</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>11.111111111111</v>
+        <v>6.25</v>
       </c>
       <c r="F17" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G17" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H17" s="15">
-        <v>-2.816901408450</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="J17" s="14">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="K17" s="15">
-        <v>6.077348066298</v>
+        <v>6.598984771573</v>
       </c>
       <c r="L17" s="15">
-        <v>23.870967741935</v>
+        <v>24.260355029585</v>
       </c>
       <c r="M17" s="15">
-        <v>137.037037037037</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.477611940298</v>
+        <v>-4.545454545454</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>42.857142857142</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.714285714285</v>
+        <v>-15</v>
       </c>
       <c r="M18" s="15">
-        <v>11.111111111111</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.384288747346</v>
+        <v>-89.717741935483</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.315789473684</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.354838709677</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J19" s="14">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.534246575342</v>
+        <v>-6.962025316455</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.094339622641</v>
+        <v>-15.517241379310</v>
       </c>
       <c r="M19" s="15">
-        <v>159.615384615385</v>
+        <v>153.448275862069</v>
       </c>
       <c r="N19" s="15">
-        <v>-29.319371727748</v>
+        <v>-27.941176470588</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-11.764705882352</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.276595744680</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.777777777777</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>54.166666666666</v>
+        <v>60</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.647302904564</v>
+        <v>-84.674329501915</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>1.851851851851</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="F21" s="17">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="G21" s="17">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H21" s="18">
-        <v>1.047120418848</v>
+        <v>5.291005291005</v>
       </c>
       <c r="I21" s="17">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="J21" s="17">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="K21" s="18">
-        <v>4.828973843058</v>
+        <v>4.788213627992</v>
       </c>
       <c r="L21" s="18">
-        <v>6.762295081967</v>
+        <v>7.156308851224</v>
       </c>
       <c r="M21" s="18">
-        <v>79.037800687285</v>
+        <v>75.076923076923</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.595539481615</v>
+        <v>-67.997750281214</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>42.857142857142</v>
+        <v>50</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>26.315789473684</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>52.542372881355</v>
+        <v>17.073170731707</v>
       </c>
       <c r="I24" s="14">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="K24" s="15">
-        <v>32.432432432432</v>
+        <v>20.179372197309</v>
       </c>
       <c r="L24" s="15">
-        <v>15.023474178403</v>
+        <v>1.132075471698</v>
       </c>
       <c r="M24" s="15">
-        <v>15.023474178403</v>
+        <v>16.521739130434</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.5</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.647058823529</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.666666666666</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L25" s="15">
-        <v>-10.638297872340</v>
+        <v>-45.679012345679</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-4.545454545454</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G26" s="14">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="H26" s="15">
-        <v>17.948717948717</v>
+        <v>62.295081967213</v>
       </c>
       <c r="I26" s="14">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="J26" s="14">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="K26" s="15">
-        <v>24.043715846994</v>
+        <v>30.729166666666</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.276679841897</v>
+        <v>-10.035842293906</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.835341365461</v>
+        <v>-11.307420494699</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
       </c>
       <c r="E27" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F27" s="14">
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
+        <v>10</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-40</v>
+      </c>
+      <c r="I27" s="14">
+        <v>14</v>
+      </c>
+      <c r="J27" s="14">
+        <v>14</v>
+      </c>
+      <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="14">
-        <v>5</v>
-      </c>
-      <c r="G27" s="14">
-        <v>8</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-37.5</v>
-      </c>
-      <c r="I27" s="14">
-        <v>13</v>
-      </c>
-      <c r="J27" s="14">
-        <v>11</v>
-      </c>
-      <c r="K27" s="15">
-        <v>18.181818181818</v>
-      </c>
       <c r="L27" s="15">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>166.666666666667</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>58.333333333333</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>11.764705882352</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.857142857142</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>10</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="M15" s="15">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="N15" s="15">
-        <v>-8.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>266.666666666667</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>111.111111111111</v>
+        <v>73.076923076923</v>
       </c>
       <c r="I16" s="14">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J16" s="14">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K16" s="15">
-        <v>28.571428571428</v>
+        <v>22.916666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>54.285714285714</v>
+        <v>49.367088607594</v>
       </c>
       <c r="M16" s="15">
-        <v>13.684210526315</v>
+        <v>11.320754716981</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.085814360770</v>
+        <v>-80.655737704918</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>24</v>
+      </c>
+      <c r="D17" s="14">
         <v>17</v>
       </c>
-      <c r="D17" s="14">
-        <v>16</v>
-      </c>
       <c r="E17" s="15">
-        <v>6.25</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F17" s="14">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="G17" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.333333333333</v>
+        <v>9.210526315789</v>
       </c>
       <c r="I17" s="14">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="J17" s="14">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="K17" s="15">
-        <v>6.598984771573</v>
+        <v>9.813084112149</v>
       </c>
       <c r="L17" s="15">
-        <v>24.260355029585</v>
+        <v>27.027027027027</v>
       </c>
       <c r="M17" s="15">
-        <v>133.333333333333</v>
+        <v>142.268041237113</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.545454545454</v>
+        <v>-2.489626556016</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>63.636363636363</v>
       </c>
       <c r="I18" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>41.666666666666</v>
+        <v>43.589743589743</v>
       </c>
       <c r="L18" s="15">
-        <v>-15</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="M18" s="15">
-        <v>-3.773584905660</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.717741935483</v>
+        <v>-89.762340036563</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.259259259259</v>
+        <v>9.615384615384</v>
       </c>
       <c r="I19" s="14">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="J19" s="14">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.962025316455</v>
+        <v>-0.598802395209</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.517241379310</v>
+        <v>-9.782608695652</v>
       </c>
       <c r="M19" s="15">
-        <v>153.448275862069</v>
+        <v>167.741935483871</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.941176470588</v>
+        <v>-24.200913242009</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-72.727272727272</v>
+        <v>300</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
         <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-29.166666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.034482758620</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.666666666666</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M20" s="15">
-        <v>60</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.674329501915</v>
+        <v>-82.978723404255</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>70</v>
+      </c>
+      <c r="D21" s="17">
         <v>45</v>
       </c>
-      <c r="D21" s="17">
-        <v>46</v>
-      </c>
       <c r="E21" s="18">
-        <v>-2.173913043478</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="G21" s="17">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H21" s="18">
-        <v>5.291005291005</v>
+        <v>17.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>569</v>
+        <v>640</v>
       </c>
       <c r="J21" s="17">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="K21" s="18">
-        <v>4.788213627992</v>
+        <v>8.843537414965</v>
       </c>
       <c r="L21" s="18">
-        <v>7.156308851224</v>
+        <v>12.084063047285</v>
       </c>
       <c r="M21" s="18">
-        <v>75.076923076923</v>
+        <v>81.303116147308</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.997750281214</v>
+        <v>-66.804979253112</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>11</v>
@@ -1207,10 +1207,10 @@
         <v>266.666666666667</v>
       </c>
       <c r="L22" s="15">
-        <v>57.142857142857</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>120</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="M23" s="15">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-39.473684210526</v>
+        <v>-12</v>
       </c>
       <c r="F24" s="14">
         <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>17.073170731707</v>
+        <v>1.052631578947</v>
       </c>
       <c r="I24" s="14">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="J24" s="14">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="K24" s="15">
-        <v>20.179372197309</v>
+        <v>16.935483870967</v>
       </c>
       <c r="L24" s="15">
-        <v>1.132075471698</v>
+        <v>2.473498233215</v>
       </c>
       <c r="M24" s="15">
-        <v>16.521739130434</v>
+        <v>18.367346938775</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-84.615384615384</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
-        <v>-55.172413793103</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.137931034482</v>
+        <v>-28.787878787878</v>
       </c>
       <c r="L25" s="15">
-        <v>-45.679012345679</v>
+        <v>-48.913043478260</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>166.666666666667</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G26" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H26" s="15">
-        <v>62.295081967213</v>
+        <v>50.746268656716</v>
       </c>
       <c r="I26" s="14">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="J26" s="14">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="K26" s="15">
-        <v>30.729166666666</v>
+        <v>32.380952380952</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.035842293906</v>
+        <v>-4.794520547945</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.307420494699</v>
+        <v>-8.250825082508</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,13 +1385,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
@@ -1403,16 +1403,16 @@
         <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.545454545454</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-57.142857142857</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M29" s="15">
-        <v>-70</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-89.189189189189</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-50</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I30" s="14">
+        <v>4</v>
+      </c>
+      <c r="J30" s="14">
+        <v>4</v>
+      </c>
+      <c r="K30" s="15">
         <v>0</v>
       </c>
-      <c r="I30" s="14">
-        <v>3</v>
-      </c>
-      <c r="J30" s="14">
-        <v>2</v>
-      </c>
-      <c r="K30" s="15">
-        <v>50</v>
-      </c>
       <c r="L30" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-70</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.322580645161</v>
+        <v>-88.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
+        <v>14</v>
+      </c>
+      <c r="J15" s="14">
         <v>13</v>
       </c>
-      <c r="J15" s="14">
-        <v>12</v>
-      </c>
       <c r="K15" s="15">
-        <v>8.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L15" s="15">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="M15" s="15">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>-13.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-8.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>73.076923076923</v>
+        <v>59.259259259259</v>
       </c>
       <c r="I16" s="14">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="J16" s="14">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K16" s="15">
-        <v>22.916666666666</v>
+        <v>23.300970873786</v>
       </c>
       <c r="L16" s="15">
-        <v>49.367088607594</v>
+        <v>49.411764705882</v>
       </c>
       <c r="M16" s="15">
-        <v>11.320754716981</v>
+        <v>10.434782608695</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.655737704918</v>
+        <v>-80.815709969788</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>41.176470588235</v>
+        <v>90.909090909090</v>
       </c>
       <c r="F17" s="14">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G17" s="14">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="H17" s="15">
-        <v>9.210526315789</v>
+        <v>32.258064516129</v>
       </c>
       <c r="I17" s="14">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="J17" s="14">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="K17" s="15">
-        <v>9.813084112149</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>27.027027027027</v>
+        <v>28.140703517587</v>
       </c>
       <c r="M17" s="15">
-        <v>142.268041237113</v>
+        <v>138.317757009346</v>
       </c>
       <c r="N17" s="15">
-        <v>-2.489626556016</v>
+        <v>-0.778210116731</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>63.636363636363</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>43.589743589743</v>
+        <v>32.558139534883</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.196721311475</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M18" s="15">
-        <v>-1.754385964912</v>
+        <v>-10.9375</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.762340036563</v>
+        <v>-90.484140233722</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>111.111111111111</v>
+        <v>283.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>9.615384615384</v>
+        <v>45.652173913043</v>
       </c>
       <c r="I19" s="14">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="J19" s="14">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.598802395209</v>
+        <v>9.248554913294</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.782608695652</v>
+        <v>0.531914893617</v>
       </c>
       <c r="M19" s="15">
-        <v>167.741935483871</v>
+        <v>190.769230769231</v>
       </c>
       <c r="N19" s="15">
-        <v>-24.200913242009</v>
+        <v>-22.540983606557</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
-        <v>300</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="I20" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J20" s="14">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K20" s="15">
-        <v>-20</v>
+        <v>-31.944444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.882352941176</v>
+        <v>-15.517241379310</v>
       </c>
       <c r="M20" s="15">
-        <v>77.777777777777</v>
+        <v>75</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.978723404255</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>55.555555555555</v>
+        <v>39.024390243902</v>
       </c>
       <c r="F21" s="17">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G21" s="17">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="H21" s="18">
-        <v>17.857142857142</v>
+        <v>22.580645161290</v>
       </c>
       <c r="I21" s="17">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="J21" s="17">
-        <v>588</v>
+        <v>629</v>
       </c>
       <c r="K21" s="18">
-        <v>8.843537414965</v>
+        <v>10.492845786963</v>
       </c>
       <c r="L21" s="18">
-        <v>12.084063047285</v>
+        <v>15.066225165562</v>
       </c>
       <c r="M21" s="18">
-        <v>81.303116147308</v>
+        <v>81.462140992167</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.804979253112</v>
+        <v>-66.746411483253</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1201,16 +1201,16 @@
         <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>266.666666666667</v>
+        <v>175</v>
       </c>
       <c r="L22" s="15">
         <v>22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>3</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>15</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-12</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H24" s="15">
-        <v>1.052631578947</v>
+        <v>-14</v>
       </c>
       <c r="I24" s="14">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="J24" s="14">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="K24" s="15">
-        <v>16.935483870967</v>
+        <v>15.413533834586</v>
       </c>
       <c r="L24" s="15">
-        <v>2.473498233215</v>
+        <v>-0.324675324675</v>
       </c>
       <c r="M24" s="15">
-        <v>18.367346938775</v>
+        <v>9.642857142857</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-57.142857142857</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J25" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.787878787878</v>
+        <v>-24.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>-48.913043478260</v>
+        <v>-47</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>73.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G26" s="14">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H26" s="15">
-        <v>50.746268656716</v>
+        <v>53.125</v>
       </c>
       <c r="I26" s="14">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="J26" s="14">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="K26" s="15">
-        <v>32.380952380952</v>
+        <v>35.111111111111</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.794520547945</v>
+        <v>-4.100946372239</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.250825082508</v>
+        <v>-7.878787878787</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>27.777777777777</v>
+        <v>42.105263157894</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.166666666666</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L29" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.189189189189</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
       <c r="E30" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.571428571428</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I15" s="14">
+        <v>16</v>
+      </c>
+      <c r="J15" s="14">
         <v>14</v>
       </c>
-      <c r="J15" s="14">
-        <v>13</v>
-      </c>
       <c r="K15" s="15">
-        <v>7.692307692307</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>433.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15">
-        <v>28.571428571428</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F16" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15">
-        <v>59.259259259259</v>
+        <v>13.888888888888</v>
       </c>
       <c r="I16" s="14">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="J16" s="14">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="K16" s="15">
-        <v>23.300970873786</v>
+        <v>17.948717948717</v>
       </c>
       <c r="L16" s="15">
-        <v>49.411764705882</v>
+        <v>46.808510638297</v>
       </c>
       <c r="M16" s="15">
-        <v>10.434782608695</v>
+        <v>8.661417322834</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.815709969788</v>
+        <v>-80.397727272727</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>90.909090909090</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F17" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>32.258064516129</v>
+        <v>58.928571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="J17" s="14">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="K17" s="15">
-        <v>13.333333333333</v>
+        <v>18.987341772151</v>
       </c>
       <c r="L17" s="15">
-        <v>28.140703517587</v>
+        <v>29.953917050691</v>
       </c>
       <c r="M17" s="15">
-        <v>138.317757009346</v>
+        <v>145.217391304348</v>
       </c>
       <c r="N17" s="15">
-        <v>-0.778210116731</v>
+        <v>-0.704225352112</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-15.384615384615</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="15">
-        <v>32.558139534883</v>
+        <v>37.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>-9.523809523809</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.9375</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.484140233722</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>283.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>45.652173913043</v>
+        <v>70.731707317073</v>
       </c>
       <c r="I19" s="14">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="J19" s="14">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="K19" s="15">
-        <v>9.248554913294</v>
+        <v>9.625668449197</v>
       </c>
       <c r="L19" s="15">
-        <v>0.531914893617</v>
+        <v>5.128205128205</v>
       </c>
       <c r="M19" s="15">
-        <v>190.769230769231</v>
+        <v>192.857142857143</v>
       </c>
       <c r="N19" s="15">
-        <v>-22.540983606557</v>
+        <v>-19.921875</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-83.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>-48.387096774193</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I20" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J20" s="14">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.944444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.517241379310</v>
+        <v>-15.625</v>
       </c>
       <c r="M20" s="15">
-        <v>75</v>
+        <v>92.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.333333333333</v>
+        <v>-82.524271844660</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>39.024390243902</v>
+        <v>21.153846153846</v>
       </c>
       <c r="F21" s="17">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G21" s="17">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H21" s="18">
-        <v>22.580645161290</v>
+        <v>29.347826086956</v>
       </c>
       <c r="I21" s="17">
-        <v>695</v>
+        <v>761</v>
       </c>
       <c r="J21" s="17">
-        <v>629</v>
+        <v>681</v>
       </c>
       <c r="K21" s="18">
-        <v>10.492845786963</v>
+        <v>11.747430249632</v>
       </c>
       <c r="L21" s="18">
-        <v>15.066225165562</v>
+        <v>17.076923076923</v>
       </c>
       <c r="M21" s="18">
-        <v>81.462140992167</v>
+        <v>85.158150851581</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.746411483253</v>
+        <v>-66.041945560017</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
-      </c>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
-      <c r="H23" s="15">
-        <v>66.666666666666</v>
+        <v>6</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>66.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="L23" s="15">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="M23" s="15">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.111111111111</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="F24" s="14">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-14</v>
+        <v>-28.703703703703</v>
       </c>
       <c r="I24" s="14">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="J24" s="14">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15">
-        <v>15.413533834586</v>
+        <v>9.897610921501</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.324675324675</v>
+        <v>0.940438871473</v>
       </c>
       <c r="M24" s="15">
-        <v>9.642857142857</v>
+        <v>5.573770491803</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
         <v>6</v>
       </c>
-      <c r="D25" s="14">
-        <v>4</v>
-      </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.515151515151</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="I25" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J25" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.285714285714</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L25" s="15">
-        <v>-47</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>73.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
         <v>98</v>
       </c>
       <c r="G26" s="14">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>53.125</v>
+        <v>63.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="J26" s="14">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="K26" s="15">
-        <v>35.111111111111</v>
+        <v>33.744855967078</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.100946372239</v>
+        <v>-4.970760233918</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.878787878787</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F27" s="14">
         <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>22</v>
+      </c>
+      <c r="J27" s="14">
         <v>19</v>
       </c>
-      <c r="J27" s="14">
-        <v>17</v>
-      </c>
       <c r="K27" s="15">
-        <v>11.764705882352</v>
+        <v>15.789473684210</v>
       </c>
       <c r="L27" s="15">
-        <v>90</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
@@ -1444,16 +1444,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>42.105263157894</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>3.846153846153</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N29" s="15">
-        <v>-90</v>
+        <v>-89.583333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L30" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M30" s="15">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.473684210526</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -854,32 +854,32 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>4</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>300</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M14" s="15">
         <v>100</v>
@@ -890,25 +890,25 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="I15" s="14">
         <v>16</v>
@@ -920,13 +920,13 @@
         <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>220</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
         <v>433.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G16" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15">
-        <v>13.888888888888</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J16" s="14">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K16" s="15">
-        <v>17.948717948717</v>
+        <v>18.699186991869</v>
       </c>
       <c r="L16" s="15">
-        <v>46.808510638297</v>
+        <v>44.554455445544</v>
       </c>
       <c r="M16" s="15">
-        <v>8.661417322834</v>
+        <v>6.569343065693</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.397727272727</v>
+        <v>-80.054644808743</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>116.666666666667</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F17" s="14">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="15">
-        <v>58.928571428571</v>
+        <v>73.684210526315</v>
       </c>
       <c r="I17" s="14">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="J17" s="14">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="K17" s="15">
-        <v>18.987341772151</v>
+        <v>21.653543307086</v>
       </c>
       <c r="L17" s="15">
-        <v>29.953917050691</v>
+        <v>35.526315789473</v>
       </c>
       <c r="M17" s="15">
-        <v>145.217391304348</v>
+        <v>149.193548387097</v>
       </c>
       <c r="N17" s="15">
-        <v>-0.704225352112</v>
+        <v>0.651465798045</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J18" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>37.777777777777</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.462686567164</v>
+        <v>-1.449275362318</v>
       </c>
       <c r="M18" s="15">
-        <v>-6.060606060606</v>
+        <v>1.492537313432</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.476190476190</v>
+        <v>-90.173410404624</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>70.731707317073</v>
+        <v>67.5</v>
       </c>
       <c r="I19" s="14">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J19" s="14">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K19" s="15">
-        <v>9.625668449197</v>
+        <v>8.080808080808</v>
       </c>
       <c r="L19" s="15">
-        <v>5.128205128205</v>
+        <v>3.883495145631</v>
       </c>
       <c r="M19" s="15">
-        <v>192.857142857143</v>
+        <v>174.358974358974</v>
       </c>
       <c r="N19" s="15">
-        <v>-19.921875</v>
+        <v>-20.740740740740</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>9</v>
-      </c>
       <c r="E20" s="15">
-        <v>-44.444444444444</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-47.058823529411</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J20" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.395348837209</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.625</v>
+        <v>-11.940298507462</v>
       </c>
       <c r="M20" s="15">
-        <v>92.857142857142</v>
+        <v>90.322580645161</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.524271844660</v>
+        <v>-82.121212121212</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>21.153846153846</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F21" s="17">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G21" s="17">
         <v>184</v>
       </c>
       <c r="H21" s="18">
-        <v>29.347826086956</v>
+        <v>34.239130434782</v>
       </c>
       <c r="I21" s="17">
-        <v>761</v>
+        <v>816</v>
       </c>
       <c r="J21" s="17">
-        <v>681</v>
+        <v>727</v>
       </c>
       <c r="K21" s="18">
-        <v>11.747430249632</v>
+        <v>12.242090784044</v>
       </c>
       <c r="L21" s="18">
-        <v>17.076923076923</v>
+        <v>18.950437317784</v>
       </c>
       <c r="M21" s="18">
-        <v>85.158150851581</v>
+        <v>84.615384615384</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.041945560017</v>
+        <v>-65.598650927487</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="14">
         <v>6</v>
@@ -1236,25 +1236,25 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>77.777777777777</v>
+        <v>100</v>
       </c>
       <c r="L23" s="15">
         <v>100</v>
       </c>
       <c r="M23" s="15">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-40.740740740740</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F24" s="14">
         <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.703703703703</v>
+        <v>-13.483146067415</v>
       </c>
       <c r="I24" s="14">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="J24" s="14">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="K24" s="15">
-        <v>9.897610921501</v>
+        <v>10.576923076923</v>
       </c>
       <c r="L24" s="15">
-        <v>0.940438871473</v>
+        <v>0</v>
       </c>
       <c r="M24" s="15">
-        <v>5.573770491803</v>
+        <v>8.150470219435</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
         <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-54.838709677419</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J25" s="14">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.315789473684</v>
+        <v>-24.358974358974</v>
       </c>
       <c r="L25" s="15">
-        <v>-46.153846153846</v>
+        <v>-49.137931034482</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,63 +1344,63 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>73.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G26" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H26" s="15">
-        <v>63.333333333333</v>
+        <v>43.939393939393</v>
       </c>
       <c r="I26" s="14">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="J26" s="14">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="K26" s="15">
-        <v>33.744855967078</v>
+        <v>34.108527131782</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.970760233918</v>
+        <v>-4.419889502762</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.142857142857</v>
+        <v>-7.238605898123</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I27" s="14">
         <v>22</v>
@@ -1412,13 +1412,13 @@
         <v>15.789473684210</v>
       </c>
       <c r="L27" s="15">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,119 +1429,119 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>31.818181818181</v>
       </c>
       <c r="L28" s="15">
-        <v>-3.448275862068</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H29" s="15">
-        <v>-57.142857142857</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>-44.444444444444</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-61.538461538461</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.583333333333</v>
+        <v>-90.196078431372</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>-40</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-28.571428571428</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L30" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-61.538461538461</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-89.583333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>75</v>

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>4</v>
@@ -885,48 +885,48 @@
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-76.470588235294</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>14.285714285714</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>166.666666666667</v>
+        <v>157.142857142857</v>
       </c>
       <c r="M15" s="15">
-        <v>433.333333333333</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J16" s="14">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K16" s="15">
-        <v>18.699186991869</v>
+        <v>9.420289855072</v>
       </c>
       <c r="L16" s="15">
-        <v>44.554455445544</v>
+        <v>41.121495327102</v>
       </c>
       <c r="M16" s="15">
-        <v>6.569343065693</v>
+        <v>7.092198581560</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.054644808743</v>
+        <v>-80.312907431551</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>35.294117647058</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" s="14">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>73.684210526315</v>
+        <v>78.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="J17" s="14">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="K17" s="15">
-        <v>21.653543307086</v>
+        <v>23.703703703703</v>
       </c>
       <c r="L17" s="15">
-        <v>35.526315789473</v>
+        <v>38.016528925619</v>
       </c>
       <c r="M17" s="15">
-        <v>149.193548387097</v>
+        <v>156.923076923077</v>
       </c>
       <c r="N17" s="15">
-        <v>0.651465798045</v>
+        <v>-2.623906705539</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-16.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>6.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>33.333333333333</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>-1.449275362318</v>
+        <v>-1.428571428571</v>
       </c>
       <c r="M18" s="15">
-        <v>1.492537313432</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.173410404624</v>
+        <v>-90.534979423868</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
         <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>67.5</v>
+        <v>40</v>
       </c>
       <c r="I19" s="14">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="J19" s="14">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K19" s="15">
-        <v>8.080808080808</v>
+        <v>7.246376811594</v>
       </c>
       <c r="L19" s="15">
-        <v>3.883495145631</v>
+        <v>1.834862385321</v>
       </c>
       <c r="M19" s="15">
-        <v>174.358974358974</v>
+        <v>158.139534883721</v>
       </c>
       <c r="N19" s="15">
-        <v>-20.740740740740</v>
+        <v>-24.745762711864</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>-28.571428571428</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I20" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J20" s="14">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.395348837209</v>
+        <v>-34.375</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.940298507462</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="M20" s="15">
-        <v>90.322580645161</v>
+        <v>65.789473684210</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.121212121212</v>
+        <v>-81.686046511627</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>4.347826086956</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="F21" s="17">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="G21" s="17">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H21" s="18">
-        <v>34.239130434782</v>
+        <v>15.025906735751</v>
       </c>
       <c r="I21" s="17">
-        <v>816</v>
+        <v>861</v>
       </c>
       <c r="J21" s="17">
-        <v>727</v>
+        <v>781</v>
       </c>
       <c r="K21" s="18">
-        <v>12.242090784044</v>
+        <v>10.243277848911</v>
       </c>
       <c r="L21" s="18">
-        <v>18.950437317784</v>
+        <v>18.922651933701</v>
       </c>
       <c r="M21" s="18">
-        <v>84.615384615384</v>
+        <v>83.582089552238</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.598650927487</v>
+        <v>-65.900990099009</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>71.428571428571</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>100</v>
+        <v>111.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>100</v>
+        <v>111.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>200</v>
+        <v>216.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>21.052631578947</v>
+        <v>64.285714285714</v>
       </c>
       <c r="F24" s="14">
         <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.483146067415</v>
+        <v>-1.282051282051</v>
       </c>
       <c r="I24" s="14">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="J24" s="14">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="K24" s="15">
-        <v>10.576923076923</v>
+        <v>12.883435582822</v>
       </c>
       <c r="L24" s="15">
-        <v>0</v>
+        <v>1.657458563535</v>
       </c>
       <c r="M24" s="15">
-        <v>8.150470219435</v>
+        <v>10.843373493975</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>-30</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I25" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J25" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.358974358974</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="L25" s="15">
-        <v>-49.137931034482</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>29</v>
+      </c>
+      <c r="D26" s="14">
         <v>26</v>
       </c>
-      <c r="D26" s="14">
-        <v>15</v>
-      </c>
       <c r="E26" s="15">
-        <v>73.333333333333</v>
+        <v>11.538461538461</v>
       </c>
       <c r="F26" s="14">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G26" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H26" s="15">
-        <v>43.939393939393</v>
+        <v>32.432432432432</v>
       </c>
       <c r="I26" s="14">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="J26" s="14">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="K26" s="15">
-        <v>34.108527131782</v>
+        <v>32.042253521126</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.419889502762</v>
+        <v>-4.092071611253</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.238605898123</v>
+        <v>-6.716417910447</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>15.789473684210</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>57.142857142857</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>31.818181818181</v>
+        <v>20</v>
       </c>
       <c r="L28" s="15">
-        <v>-3.333333333333</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>-77.777777777777</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
@@ -1494,13 +1494,13 @@
         <v>-54.545454545454</v>
       </c>
       <c r="L29" s="15">
-        <v>-58.333333333333</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M29" s="15">
-        <v>-61.538461538461</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.196078431372</v>
+        <v>-90.566037735849</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H30" s="15">
-        <v>-71.428571428571</v>
+        <v>-80</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1535,13 +1535,13 @@
         <v>-44.444444444444</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M30" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.583333333333</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>75</v>

--- a/data/source/weekly/cs-en-us-046pct.xlsx
+++ b/data/source/weekly/cs-en-us-046pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -879,13 +879,13 @@
         <v>300</v>
       </c>
       <c r="L14" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="M14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-78.947368421052</v>
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L15" s="15">
-        <v>157.142857142857</v>
+        <v>185.714285714286</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-35.714285714285</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.428571428571</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="I16" s="14">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J16" s="14">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K16" s="15">
-        <v>9.420289855072</v>
+        <v>9.589041095890</v>
       </c>
       <c r="L16" s="15">
-        <v>41.121495327102</v>
+        <v>41.592920353982</v>
       </c>
       <c r="M16" s="15">
-        <v>7.092198581560</v>
+        <v>8.108108108108</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.312907431551</v>
+        <v>-80.074719800747</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H17" s="15">
-        <v>78.571428571428</v>
+        <v>56.923076923076</v>
       </c>
       <c r="I17" s="14">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="J17" s="14">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="K17" s="15">
-        <v>23.703703703703</v>
+        <v>24.827586206896</v>
       </c>
       <c r="L17" s="15">
-        <v>38.016528925619</v>
+        <v>43.083003952569</v>
       </c>
       <c r="M17" s="15">
-        <v>156.923076923077</v>
+        <v>153.146853146853</v>
       </c>
       <c r="N17" s="15">
-        <v>-2.623906705539</v>
+        <v>-1.362397820163</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I18" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>27.777777777777</v>
+        <v>33.928571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-1.428571428571</v>
+        <v>5.633802816901</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.534979423868</v>
+        <v>-90.144546649145</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="J19" s="14">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K19" s="15">
-        <v>7.246376811594</v>
+        <v>2.222222222222</v>
       </c>
       <c r="L19" s="15">
-        <v>1.834862385321</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="M19" s="15">
-        <v>158.139534883721</v>
+        <v>152.747252747253</v>
       </c>
       <c r="N19" s="15">
-        <v>-24.745762711864</v>
+        <v>-29.012345679012</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-55.555555555555</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J20" s="14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K20" s="15">
-        <v>-34.375</v>
+        <v>-31</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.267605633802</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="M20" s="15">
-        <v>65.789473684210</v>
+        <v>64.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.686046511627</v>
+        <v>-80.833333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.518518518518</v>
+        <v>-1.785714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G21" s="17">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H21" s="18">
-        <v>15.025906735751</v>
+        <v>2.884615384615</v>
       </c>
       <c r="I21" s="17">
-        <v>861</v>
+        <v>920</v>
       </c>
       <c r="J21" s="17">
-        <v>781</v>
+        <v>837</v>
       </c>
       <c r="K21" s="18">
-        <v>10.243277848911</v>
+        <v>9.916367980884</v>
       </c>
       <c r="L21" s="18">
-        <v>18.922651933701</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M21" s="18">
-        <v>83.582089552238</v>
+        <v>82.539682539682</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.900990099009</v>
+        <v>-65.465465465465</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M22" s="15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>500</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>111.111111111111</v>
+        <v>110</v>
       </c>
       <c r="L23" s="15">
-        <v>111.111111111111</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>216.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>64.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.282051282051</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="I24" s="14">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="J24" s="14">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="K24" s="15">
-        <v>12.883435582822</v>
+        <v>9.798270893371</v>
       </c>
       <c r="L24" s="15">
-        <v>1.657458563535</v>
+        <v>2.972972972972</v>
       </c>
       <c r="M24" s="15">
-        <v>10.843373493975</v>
+        <v>11.403508771929</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>600</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>46.153846153846</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I25" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J25" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.455696202531</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="L25" s="15">
-        <v>-45.454545454545</v>
+        <v>-43.442622950819</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>11.538461538461</v>
+        <v>-5</v>
       </c>
       <c r="F26" s="14">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G26" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>32.432432432432</v>
+        <v>20.253164556962</v>
       </c>
       <c r="I26" s="14">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="J26" s="14">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="K26" s="15">
-        <v>32.042253521126</v>
+        <v>29.605263157894</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.092071611253</v>
+        <v>-3.431372549019</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.716417910447</v>
+        <v>-8.796296296296</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I27" s="14">
+        <v>26</v>
+      </c>
+      <c r="J27" s="14">
         <v>24</v>
       </c>
-      <c r="J27" s="14">
-        <v>20</v>
-      </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>73.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>10.714285714285</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" s="15">
-        <v>-83.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-64.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.566037735849</v>
+        <v>-90.740740740740</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1529,19 +1529,19 @@
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-64.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-90.196078431372</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
